--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452243</v>
+        <v>123452695</v>
       </c>
       <c r="B2" t="n">
-        <v>94781</v>
+        <v>96573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spetsig rörsvepemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Liochlaena subulata s.str.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(A.Evans) Schljakov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452695</v>
+        <v>123452243</v>
       </c>
       <c r="B3" t="n">
-        <v>96567</v>
+        <v>94787</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>897</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spetsig rörsvepemossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Liochlaena subulata s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Evans) Schljakov</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452695</v>
+        <v>123452243</v>
       </c>
       <c r="B2" t="n">
-        <v>96576</v>
+        <v>94807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>897</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spetsig rörsvepemossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Liochlaena subulata s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Evans) Schljakov</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452243</v>
+        <v>123452695</v>
       </c>
       <c r="B3" t="n">
-        <v>94790</v>
+        <v>96593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spetsig rörsvepemossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Liochlaena subulata s.str.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(A.Evans) Schljakov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452243</v>
       </c>
       <c r="B2" t="n">
-        <v>94807</v>
+        <v>94813</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123452695</v>
       </c>
       <c r="B3" t="n">
-        <v>96593</v>
+        <v>96609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452243</v>
       </c>
       <c r="B2" t="n">
-        <v>94813</v>
+        <v>94815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123452695</v>
       </c>
       <c r="B3" t="n">
-        <v>96609</v>
+        <v>96611</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452243</v>
+        <v>123452695</v>
       </c>
       <c r="B2" t="n">
-        <v>94815</v>
+        <v>96611</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spetsig rörsvepemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Liochlaena subulata s.str.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(A.Evans) Schljakov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452695</v>
+        <v>123452243</v>
       </c>
       <c r="B3" t="n">
-        <v>96611</v>
+        <v>94815</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>897</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spetsig rörsvepemossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Liochlaena subulata s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Evans) Schljakov</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123452695</v>
       </c>
       <c r="B2" t="n">
-        <v>96611</v>
+        <v>96651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123452243</v>
       </c>
       <c r="B3" t="n">
-        <v>94815</v>
+        <v>95323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452695</v>
+        <v>123452243</v>
       </c>
       <c r="B2" t="n">
-        <v>96651</v>
+        <v>95323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>897</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spetsig rörsvepemossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Liochlaena subulata s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Evans) Schljakov</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452243</v>
+        <v>123452695</v>
       </c>
       <c r="B3" t="n">
-        <v>95323</v>
+        <v>96651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spetsig rörsvepemossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Liochlaena subulata s.str.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(A.Evans) Schljakov</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 49890-2024 artfynd.xlsx
+++ b/artfynd/A 49890-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452243</v>
+        <v>123452695</v>
       </c>
       <c r="B2" t="n">
-        <v>95323</v>
+        <v>96651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>897</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spetsig rörsvepemossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Liochlaena subulata s.str.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(A.Evans) Schljakov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452695</v>
+        <v>123452243</v>
       </c>
       <c r="B3" t="n">
-        <v>96651</v>
+        <v>95323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>897</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spetsig rörsvepemossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Liochlaena subulata s.str.</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Evans) Schljakov</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
